--- a/mental_health_forms/005_impact_of_isolation_on_life_survey--mental_health_forms.xlsx
+++ b/mental_health_forms/005_impact_of_isolation_on_life_survey--mental_health_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -799,7 +799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C53"/>
+  <dimension ref="A1:C52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -951,12 +951,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>partner</t>
+          <t>ex-partner</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Partner</t>
+          <t>Ex-partner</t>
         </is>
       </c>
     </row>
@@ -968,12 +968,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ex-partner</t>
+          <t>family_member</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ex-partner</t>
+          <t>Family member</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>family_member</t>
+          <t>friend</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Family member</t>
+          <t>Friend</t>
         </is>
       </c>
     </row>
@@ -1002,29 +1002,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>friend</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Friend</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>relationship_type_choices</t>
+          <t>loneliness_level_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1-2_days</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1-2 days</t>
         </is>
       </c>
     </row>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1-2_days</t>
+          <t>3-4_days</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1-2 days</t>
+          <t>3-4 days</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>3-4_days</t>
+          <t>5-7_days</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>3-4 days</t>
+          <t>5-7 days</t>
         </is>
       </c>
     </row>
@@ -1087,29 +1087,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5-7_days</t>
+          <t>almost_every_day</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>5-7 days</t>
+          <t>Almost every day</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>loneliness_level_choices</t>
+          <t>social_support_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>almost_every_day</t>
+          <t>family</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Almost every day</t>
+          <t>Family</t>
         </is>
       </c>
     </row>
@@ -1121,12 +1121,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>family</t>
+          <t>friends</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Family</t>
+          <t>Friends</t>
         </is>
       </c>
     </row>
@@ -1138,12 +1138,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>friends</t>
+          <t>community</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>Community</t>
         </is>
       </c>
     </row>
@@ -1155,12 +1155,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>community</t>
+          <t>online_community</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Community</t>
+          <t>Online community</t>
         </is>
       </c>
     </row>
@@ -1172,29 +1172,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>online_community</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Online community</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>social_support_choices</t>
+          <t>coping_mechanism_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>talk_to_friends_or_family</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Talk to friends or family</t>
         </is>
       </c>
     </row>
@@ -1206,12 +1206,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>talk_to_friends_or_family</t>
+          <t>exercise</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Talk to friends or family</t>
+          <t>Exercise</t>
         </is>
       </c>
     </row>
@@ -1223,12 +1223,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>exercise</t>
+          <t>hobbies</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Exercise</t>
+          <t>Hobbies</t>
         </is>
       </c>
     </row>
@@ -1240,12 +1240,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>hobbies</t>
+          <t>watching_movies_or_tv_shows</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Hobbies</t>
+          <t>Watching movies or TV shows</t>
         </is>
       </c>
     </row>
@@ -1257,12 +1257,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>watching_movies_or_tv_shows</t>
+          <t>sleeping</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Watching movies or TV shows</t>
+          <t>Sleeping</t>
         </is>
       </c>
     </row>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>sleeping</t>
+          <t>reading</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sleeping</t>
+          <t>Reading</t>
         </is>
       </c>
     </row>
@@ -1291,29 +1291,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>reading</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>coping_mechanism_choices</t>
+          <t>life_change_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1325,29 +1325,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>life_change_choices</t>
+          <t>emotional_change_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>better</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Better</t>
         </is>
       </c>
     </row>
@@ -1359,12 +1359,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>better</t>
+          <t>worse</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Better</t>
+          <t>Worse</t>
         </is>
       </c>
     </row>
@@ -1376,29 +1376,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>worse</t>
+          <t>about_the_same</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Worse</t>
+          <t>About the same</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>emotional_change_choices</t>
+          <t>sleep_quality_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>about_the_same</t>
+          <t>better</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>About the same</t>
+          <t>Better</t>
         </is>
       </c>
     </row>
@@ -1410,12 +1410,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>better</t>
+          <t>worse</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Better</t>
+          <t>Worse</t>
         </is>
       </c>
     </row>
@@ -1427,29 +1427,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>worse</t>
+          <t>about_the_same</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Worse</t>
+          <t>About the same</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>sleep_quality_choices</t>
+          <t>physical_health_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>about_the_same</t>
+          <t>much_better</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>About the same</t>
+          <t>Much better</t>
         </is>
       </c>
     </row>
@@ -1461,12 +1461,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>much_better</t>
+          <t>a_bit_better</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Much better</t>
+          <t>A bit better</t>
         </is>
       </c>
     </row>
@@ -1478,12 +1478,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>a_bit_better</t>
+          <t>about_the_same</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>A bit better</t>
+          <t>About the same</t>
         </is>
       </c>
     </row>
@@ -1495,12 +1495,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>about_the_same</t>
+          <t>a_bit_worse</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>About the same</t>
+          <t>A bit worse</t>
         </is>
       </c>
     </row>
@@ -1512,29 +1512,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>a_bit_worse</t>
+          <t>much_worse</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>A bit worse</t>
+          <t>Much worse</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>physical_health_choices</t>
+          <t>mental_health_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>much_worse</t>
+          <t>much_better</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Much worse</t>
+          <t>Much better</t>
         </is>
       </c>
     </row>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>much_better</t>
+          <t>a_bit_better</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Much better</t>
+          <t>A bit better</t>
         </is>
       </c>
     </row>
@@ -1563,12 +1563,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>a_bit_better</t>
+          <t>about_the_same</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>A bit better</t>
+          <t>About the same</t>
         </is>
       </c>
     </row>
@@ -1580,12 +1580,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>about_the_same</t>
+          <t>a_bit_worse</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>About the same</t>
+          <t>A bit worse</t>
         </is>
       </c>
     </row>
@@ -1597,29 +1597,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>a_bit_worse</t>
+          <t>much_worse</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>A bit worse</t>
+          <t>Much worse</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>mental_health_choices</t>
+          <t>anxiety_level_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>much_worse</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Much worse</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1631,12 +1631,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1-2</t>
         </is>
       </c>
     </row>
@@ -1648,12 +1648,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>3-4</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>3-4</t>
         </is>
       </c>
     </row>
@@ -1665,12 +1665,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>3-4</t>
+          <t>5-7</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>3-4</t>
+          <t>5-7</t>
         </is>
       </c>
     </row>
@@ -1682,27 +1682,10 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>5-7</t>
+          <t>8-10</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
-        <is>
-          <t>5-7</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>anxiety_level_choices</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>8-10</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
         <is>
           <t>8-10</t>
         </is>
